--- a/constructs.xlsx
+++ b/constructs.xlsx
@@ -6556,7 +6556,7 @@
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>spectrum</t>
+          <t>deep</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
@@ -6582,6 +6582,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
         <is>
@@ -6674,6 +6675,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
         <is>
@@ -6745,6 +6747,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="12" t="inlineStr">
         <is>
@@ -6829,6 +6832,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="12" t="inlineStr">
         <is>
